--- a/survey_templates/031_financial_knowledge_survey_averhart--survey_templates.xlsx
+++ b/survey_templates/031_financial_knowledge_survey_averhart--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please read this carefully before continuing.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,138 +542,162 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demographics</t>
+          <t>level_of_knowledge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>demographics</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Your Level of Knowledge</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select your level of knowledge about personal finance.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>financial_knowledge_questions</t>
+          <t>financial_goals</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>financial_knowledge_questions</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Your Short-Term Financial Goals</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please describe your financial goals for the next 6-12 months.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>financial_knowledge</t>
+          <t>financial_institutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>financial_knowledge</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Financial Institution Familiarity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select the financial institution(s) you are familiar with.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>financial_literacy_questions</t>
+          <t>financial_products</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>financial_literacy_questions</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Financial Products and Services Used</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select all the financial products or services you have used in the past 6-12 months.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>financial_literacy</t>
+          <t>debt_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>financial_literacy</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Debt Management</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How do you currently manage your debt?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>financial_knowledge_level</t>
+          <t>financial_crisis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>financial_knowledge_level</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Financial Crisis or Emergency</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Have you ever experienced a financial crisis or emergency?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>knowledge_about_investments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Knowledge about Investments and Saving Strategies</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please rate your level of knowledge about investment and saving strategies.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>institutional_meeting_financial_needs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Does our Financial Institution Meet Your Needs?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please rate how well our institution meets your financial needs.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>current_financial_situation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Your Current Financial Situation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please rate your satisfaction with your current financial situation.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,23 +785,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>submission_status</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Submission Status</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select the status of your submission.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Submission Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select the date of your submission.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Submission Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select the time of your submission.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Any Additional Comments</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments or feedback.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -837,43 +893,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submission</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Your Email</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please enter your email address.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Your Phone Number</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please enter your phone number.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submission_time</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Any Notes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide any additional notes or comments.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,108 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Email 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please enter your email address.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>submission_status</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>submission_status_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>submission_status_date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1029,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1057,187 +1037,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>financial_knowledge_questions_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>i_am_highly_knowledgeable</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>I am highly knowledgeable</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>financial_knowledge_questions_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>i_have_some_knowledge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>I have some knowledge</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>financial_literacy_questions_choices</t>
+          <t>level_of_knowledge_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>i_have_little_knowledge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>I have little knowledge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>financial_literacy_questions_choices</t>
+          <t>financial_institutions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>our_bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Our bank</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>financial_literacy_questions_choices</t>
+          <t>financial_institutions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>another_bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Another bank</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>financial_institutions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>credit_union</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Credit union</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>financial_institutions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>submission_choices</t>
+          <t>financial_products_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>savings_account</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Savings account</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>financial_products_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>checking_account</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Checking account</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>financial_products_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Credit card</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>financial_products_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>loan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Loan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>financial_products_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>investment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>financial_products_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>insurance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>debt_management_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>i_have_a_clear_plan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>I have a clear plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>debt_management_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>i_try_to_pay_off_high-interest_debt_first</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>I try to pay off high-interest debt first</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>debt_management_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>i_pay_off_debt_as_it_comes</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I pay off debt as it comes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>debt_management_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>i_don't_have_a_plan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>I don't have a plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>financial_crisis_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>financial_crisis_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>submission_status_choices</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>option3</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>submission_status_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>submission_status_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
